--- a/doc/개발진척.xlsx
+++ b/doc/개발진척.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jkjus\Documents\GitHub\school_free_time\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8906879E-8650-42E5-9A6B-5372C5272023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE5E9499-C7C2-4A16-AA65-1890C780D934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="59">
   <si>
     <t>서비스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -303,6 +303,10 @@
   </si>
   <si>
     <t>추가 컨텐츠 기획</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>완료(5.12)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -310,7 +314,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -324,12 +328,6 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -787,17 +785,23 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>7</v>
+      <c r="C7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
@@ -829,17 +833,23 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D10">
-        <v>7</v>
+      <c r="D10" s="1">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">

--- a/doc/개발진척.xlsx
+++ b/doc/개발진척.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jkjus\Documents\GitHub\school_free_time\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE5E9499-C7C2-4A16-AA65-1890C780D934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B94136-9558-4254-B074-A86BC741D9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="59">
   <si>
     <t>서비스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1011,6 +1011,9 @@
       <c r="D21">
         <v>2</v>
       </c>
+      <c r="E21" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A22" t="s">

--- a/doc/개발진척.xlsx
+++ b/doc/개발진척.xlsx
@@ -8,17 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jkjus\Documents\GitHub\school_free_time\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B94136-9558-4254-B074-A86BC741D9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF16C0A5-F2FC-4BBE-B8B1-B4F4798FF2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -43,7 +54,7 @@
 하: 메뉴얼 존재</t>
       </text>
     </comment>
-    <comment ref="B12" authorId="1" shapeId="0" xr:uid="{6D16F50A-D75A-4D70-9D4B-C8959F375F92}">
+    <comment ref="B15" authorId="1" shapeId="0" xr:uid="{6D16F50A-D75A-4D70-9D4B-C8959F375F92}">
       <text>
         <t>[스레드 댓글]
 사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
@@ -51,7 +62,7 @@
     https://www.syu.ac.kr/wp-content/uploads/2018/08/vr_map_v3.jpg</t>
       </text>
     </comment>
-    <comment ref="B13" authorId="2" shapeId="0" xr:uid="{74BB8CB1-603C-463D-B31F-FDFBAE4F1D79}">
+    <comment ref="B16" authorId="2" shapeId="0" xr:uid="{74BB8CB1-603C-463D-B31F-FDFBAE4F1D79}">
       <text>
         <t>[스레드 댓글]
 사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
@@ -59,7 +70,7 @@
     제1실습관, 대강당, 바울관, 다니엘관, 등</t>
       </text>
     </comment>
-    <comment ref="B18" authorId="3" shapeId="0" xr:uid="{1C2B4D2C-0DBE-41B5-AAC8-93CF68BA2CAB}">
+    <comment ref="B21" authorId="3" shapeId="0" xr:uid="{1C2B4D2C-0DBE-41B5-AAC8-93CF68BA2CAB}">
       <text>
         <t>[스레드 댓글]
 사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
@@ -72,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="65">
   <si>
     <t>서비스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -122,18 +133,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>도서관 추천 알고리즘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>도서관 UI 개선</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>랜덤채팅 UI 개선</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>추천 건물 누끼따기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -307,6 +306,41 @@
   </si>
   <si>
     <t>완료(5.12)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도서관-1-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도서관pos cleanup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI 개선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도서관 자리추천 알고리즘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DevOps-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>How to run 개선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김성현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RedTeam-2</t>
+  </si>
+  <si>
+    <t>관리페이지 세션관리</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -651,7 +685,7 @@
 중: 프로젝트 코드이해 필요
 하: 메뉴얼 존재</text>
   </threadedComment>
-  <threadedComment ref="B12" dT="2026-05-06T09:00:12.62" personId="{FB5152E4-12D4-4B92-AF2E-050AC67B08C9}" id="{6D16F50A-D75A-4D70-9D4B-C8959F375F92}">
+  <threadedComment ref="B15" dT="2026-05-06T09:00:12.62" personId="{FB5152E4-12D4-4B92-AF2E-050AC67B08C9}" id="{6D16F50A-D75A-4D70-9D4B-C8959F375F92}">
     <text>https://www.syu.ac.kr/wp-content/uploads/2018/08/vr_map_v3.jpg</text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -660,10 +694,10 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="B13" dT="2026-05-06T09:02:06.66" personId="{FB5152E4-12D4-4B92-AF2E-050AC67B08C9}" id="{74BB8CB1-603C-463D-B31F-FDFBAE4F1D79}">
+  <threadedComment ref="B16" dT="2026-05-06T09:02:06.66" personId="{FB5152E4-12D4-4B92-AF2E-050AC67B08C9}" id="{74BB8CB1-603C-463D-B31F-FDFBAE4F1D79}">
     <text>제1실습관, 대강당, 바울관, 다니엘관, 등</text>
   </threadedComment>
-  <threadedComment ref="B18" dT="2026-05-06T09:09:58.38" personId="{FB5152E4-12D4-4B92-AF2E-050AC67B08C9}" id="{1C2B4D2C-0DBE-41B5-AAC8-93CF68BA2CAB}">
+  <threadedComment ref="B21" dT="2026-05-06T09:09:58.38" personId="{FB5152E4-12D4-4B92-AF2E-050AC67B08C9}" id="{1C2B4D2C-0DBE-41B5-AAC8-93CF68BA2CAB}">
     <text>Numpy, pandas 도입 권고</text>
   </threadedComment>
 </ThreadedComments>
@@ -671,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.296875" bestFit="1" customWidth="1"/>
@@ -684,7 +718,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -696,12 +730,12 @@
         <v>8</v>
       </c>
       <c r="F1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -716,12 +750,12 @@
         <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -735,7 +769,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -749,171 +783,180 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>41</v>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="1">
-        <v>2</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>58</v>
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13">
-        <v>8</v>
+      <c r="A13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -924,117 +967,174 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+        <v>8</v>
+      </c>
+      <c r="E16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
       </c>
       <c r="D17">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+        <v>3</v>
+      </c>
+      <c r="E17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="E18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C19" t="s">
         <v>7</v>
       </c>
       <c r="D19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="E20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s">
         <v>7</v>
-      </c>
-      <c r="D20">
-        <v>2</v>
-      </c>
-      <c r="E20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" t="s">
-        <v>5</v>
       </c>
       <c r="D21">
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D22">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>46</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
